--- a/Fase 2/Evidencias Proyecto/Evidencias de Documentación/EDT CuTuCo.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de Documentación/EDT CuTuCo.xlsx
@@ -52,7 +52,7 @@
     <t>CLP 7.438 / hora (backend); hasta 13.388 / hora como JP</t>
   </si>
   <si>
-    <t>Lo asignamos principalmente a FastAPI, microservicios, pagos con Webpay Mall (Split Payment), base de datos, Supabase, Cloud Run, Secret Manager, GitHub Actions y coordinación del proyecto.</t>
+    <t>Lo asignamos principalmente a la lógica de FastAPI para la integración con Webpay, la base de datos, Supabase (Auth, RLS, policies y grants), Cloud Run, Secret Manager, GitHub Actions y la coordinación del proyecto.</t>
   </si>
   <si>
     <t>Ignacio Fuenzalida - IT Frontend</t>
@@ -304,7 +304,7 @@
     <t>Framework backend</t>
   </si>
   <si>
-    <t>Lo usamos para exponer la API REST y separar los servicios del backend.</t>
+    <t>Lo usamos para exponer los endpoints de la integración con Webpay y mantener esa lógica separada del frontend.</t>
   </si>
   <si>
     <t>Python</t>
@@ -361,7 +361,7 @@
     <t>Modelado de datos</t>
   </si>
   <si>
-    <t>Lo usamos para modelar el DER y generar DDL.</t>
+    <t>Lo usamos para modelar el MER y generar DDL.</t>
   </si>
   <si>
     <t>DBeaver Community 26.2.0</t>
@@ -535,7 +535,7 @@
   </si>
   <si>
     <t>3.1 Preparación de backend y API
-Crear la base técnica del backend remoto, que concentrará las reglas de negocio.</t>
+Crear la base técnica del backend remoto, que resolverá la lógica específica de la integración con Webpay.</t>
   </si>
   <si>
     <t>4.1 Preparación Vue.js + Vite
@@ -583,7 +583,7 @@
   </si>
   <si>
     <t>3.3 Servicios de Cliente, Vendedor y Administración
-Dejar disponibles los datos y operaciones de cada rol, tanto con PostgREST como con FastAPI.</t>
+Dejar disponibles los datos y operaciones de cada rol con PostgREST, RLS, policies y grants, y reservar FastAPI para la integración con Webpay.</t>
   </si>
   <si>
     <t>4.3 Panel vendedor y stock
@@ -607,7 +607,7 @@
   </si>
   <si>
     <t>3.4 Pagos con Webpay Mall (Split Payment)
-Reemplazar la confirmación simulada por un flujo real con Webpay Mall, donde la pasarela captura y dispersa el pago en tiempo real sin custodia de fondos.</t>
+Reemplazar la confirmación simulada por un flujo real con Webpay Mall (Split Payment), en el que la pasarela captura y dispersa el pago en tiempo real hacia la cuenta de cada comercio.</t>
   </si>
   <si>
     <t>4.4 Panel administración y dashboard
@@ -746,7 +746,7 @@
     <t>Semana 10 - 19/11/2026</t>
   </si>
   <si>
-    <t>Checkout con Webpay Mall, dispersión (Split Payment), código de entrega, calificaciones, API y navegación crítica ejecutados y registrados.</t>
+    <t>Checkout con Webpay Mall, dispersión (Split Payment), código de entrega, calificaciones, gestión de reclamos (RF-027), API y navegación crítica ejecutados y registrados.</t>
   </si>
   <si>
     <t>6.1-6.3</t>
@@ -764,13 +764,13 @@
     <t>Semana 11 - 26/11/2026</t>
   </si>
   <si>
-    <t>Alcance verificado contra los 21 requerimientos que quedan, defectos críticos tratados y versión estable preparada para cierre.</t>
+    <t>Alcance verificado contra los 22 requerimientos vigentes (los 21 anteriores más RF-027 Gestión de Reclamos), defectos críticos tratados y versión estable preparada para cierre.</t>
   </si>
   <si>
     <t>6.4-6.5</t>
   </si>
   <si>
-    <t>Compararemos lo construido con los 21 requerimientos que quedan y comprobaremos que no haya pendientes que impidan la entrega.</t>
+    <t>Compararemos lo construido con los 22 requerimientos vigentes y comprobaremos que no haya pendientes que impidan la entrega.</t>
   </si>
   <si>
     <t>H06</t>
@@ -932,7 +932,7 @@
     <t>Definir con claridad qué problema resolveremos (la brecha tecnológica y la intermediación que afectan a los pequeños productores), qué alcance será oficial y qué quedará fuera.</t>
   </si>
   <si>
-    <t>Consolidaremos objetivo, alcance, supuestos, restricciones, integrantes y criterios de cambio. Con la revisión de los 26 requerimientos del ERS dejamos 21 dentro y 5 fuera (RF-008, RF-010, RF-013, RF-015 y RF-016), y simplificamos varios de los que quedan.</t>
+    <t>Consolidaremos objetivo, alcance, supuestos, restricciones, integrantes y criterios de cambio. Con la revisión del ERS dejamos 22 requerimientos vigentes y 5 fuera (RF-008, RF-010, RF-013, RF-015 y RF-016), incorporamos RF-027 (Gestión de Reclamos) y simplificamos varios de los que quedan.</t>
   </si>
   <si>
     <t>Semana 1</t>
@@ -1049,13 +1049,13 @@
     <t>Traducir el alcance del negocio a requisitos verificables.</t>
   </si>
   <si>
-    <t>Mantendremos el ERS con los requerimientos RF-001 a RF-026 y los requerimientos no funcionales, y marcaremos cuáles quedan y cuáles salen. Para los que quedan describiremos actores, secuencia, excepciones y criterio de aceptación; para los que salen dejaremos escrito el motivo.</t>
+    <t>Mantendremos el ERS con los requerimientos RF-001 a RF-026 más el requerimiento nuevo RF-027 (Gestión de Reclamos) y los requerimientos no funcionales, y marcaremos cuáles quedan y cuáles salen. Para los que quedan describiremos actores, secuencia, excepciones y criterio de aceptación; para los que salen dejaremos escrito el motivo.</t>
   </si>
   <si>
     <t>Semanas 2-3</t>
   </si>
   <si>
-    <t>ERS actualizado, tabla Queda / No queda con las anotaciones del nuevo alcance y matriz de trazabilidad inicial.</t>
+    <t>ERS actualizado con RF-027, tabla Queda / No queda con las anotaciones del nuevo alcance y matriz de trazabilidad inicial.</t>
   </si>
   <si>
     <t>Cada funcionalidad oficial tiene requisito y criterio de aceptación, y cada recorte tiene su justificación.</t>
@@ -1073,13 +1073,13 @@
     <t>Diseñar una estructura PostgreSQL que soporte el crecimiento funcional de CuTuCo.</t>
   </si>
   <si>
-    <t>Modelaremos en pgModeler las entidades que quedan: perfiles de usuario enlazados a Supabase Auth (con intentos_login_fallidos y bloqueado_hasta), productores (con rut_oficial y codigo_comercio_mall), productos, categorías, regiones y comunas, pedidos, ítems, payments, calificaciones, amonestaciones, lista de palabras prohibadas y delivery_tracking con código de verificación. La tabla payouts desaparece porque la dispersión la realiza la pasarela. Dejamos fuera las tablas de historial de precios, alertas de stock y evidencias fotográficas.</t>
+    <t>Modelaremos en pgModeler las entidades vigentes: perfiles de usuario enlazados a Supabase Auth (sin campos de intentos fallidos ni de bloqueo de cuenta, porque esa protección la resuelve GoTrue), productores (con rut_oficial y codigo_comercio_mall), productos, categorías, regiones y comunas, pedidos, ítems, payments, calificaciones, amonestaciones, reclamos (RF-027), lista de palabras prohibidas y delivery_tracking con código de verificación. No modelamos tablas de historial de precios, alertas de stock, evidencias fotográficas ni liquidación de fondos, porque la dispersión la realiza la pasarela.</t>
   </si>
   <si>
     <t>Semanas 2-4</t>
   </si>
   <si>
-    <t>DER/relacional y scripts DDL.</t>
+    <t>MER (modelo entidad-relación) y scripts DDL.</t>
   </si>
   <si>
     <t>Relaciones, claves, restricciones e índices definidos y coherentes, y cada tabla responde a un requerimiento que queda.</t>
@@ -1097,7 +1097,7 @@
     <t>Definir cómo se separarán frontend, backend, datos y servicios externos.</t>
   </si>
   <si>
-    <t>Documentaremos la arquitectura Opción A y la proyección Opción B, con diagramas de componentes, despliegue y secuencia (checkout, delivery, moderación y liquidación vía pasarela). Decidiremos qué consultas van directo a PostgREST y cuáles pasan por FastAPI, y dejaremos escrito qué hace Supabase Auth.</t>
+    <t>Documentaremos la arquitectura Opción A y la proyección Opción B, con diagramas de componentes, despliegue y secuencia (checkout, delivery, moderación y dispersión del pago por la pasarela). Decidiremos qué consultas van directo a PostgREST y qué resuelve FastAPI, que se limita a la lógica específica y compleja de la integración con Webpay, y dejaremos escrito qué resuelve Supabase Auth (GoTrue) y qué cubren los roles, las RLS, las policies y los grants.</t>
   </si>
   <si>
     <t>Diagramas y decisión arquitectónica.</t>
@@ -1118,7 +1118,7 @@
     <t>Diseñar las pantallas necesarias antes de construirlas.</t>
   </si>
   <si>
-    <t>Elaboraremos mockups para catálogo, carrito, checkout, registro y login, panel vendedor, panel de administración (aprobación de productores, sanciones y pagos) y seguimiento de delivery con código de verificación.</t>
+    <t>Elaboraremos mockups para catálogo, carrito, checkout, registro y login, panel vendedor, panel de administración (aprobación de postulaciones, productores y productos, gestión de reclamos RF-027, sanciones y apelaciones, y consulta de pagos), seguimiento del pedido con código de verificación y las pantallas donde el comprador registra y sigue un reclamo.</t>
   </si>
   <si>
     <t>Semanas 3-4</t>
@@ -1157,7 +1157,7 @@
     <t>Los flujos críticos tienen casos y resultados esperados, y los costos de la Opción A y de la proyección B están desglosados.</t>
   </si>
   <si>
-    <t>Priorizaremos checkout, autenticación, permisos por rol, cobertura regional y código de entrega.</t>
+    <t>Priorizaremos checkout, autenticación, permisos por rol, cobertura regional, código de entrega y gestión de reclamos.</t>
   </si>
   <si>
     <t>3.0</t>
@@ -1172,10 +1172,10 @@
     <t>Preparación de backend y API</t>
   </si>
   <si>
-    <t>Crear la base técnica del backend remoto, que concentrará las reglas de negocio.</t>
-  </si>
-  <si>
-    <t>Configuraremos FastAPI con estructura por servicios, validación mínima con Pydantic, manejo de errores, logging y configuración para Docker. FastAPI solo tendrá lo que necesita lógica propia: bloqueo de cuenta, pagos con Webpay Mall, cobertura regional, sanciones y correos de negocio. Las consultas simples irán directo a PostgREST.</t>
+    <t>Crear la base técnica del backend remoto, que resolverá la lógica específica de la integración con Webpay.</t>
+  </si>
+  <si>
+    <t>Configuraremos FastAPI con estructura por servicios, validación mínima con Pydantic, manejo de errores, logging y configuración para Docker. FastAPI se limita a la lógica específica y compleja de la integración con Webpay Mall (Split Payment): no implementamos allí autenticación, autorización, validación de formularios, correos, sanciones, cobertura regional ni CRUD. La autenticación y las autorizaciones restantes se gestionan con Supabase Auth (GoTrue) y con los controles de permisos de Supabase (roles, RLS, policies y grants). Las consultas simples y el CRUD van directo a PostgREST.</t>
   </si>
   <si>
     <t>Semanas 4-5</t>
@@ -1202,7 +1202,7 @@
     <t>Garantizar acceso seguro y permisos diferenciados.</t>
   </si>
   <si>
-    <t>Usaremos Supabase Auth (GoTrue) para registro, login, refresh de sesión, recuperación y cambio de contraseña (RF-001, RF-020, RF-023 y RF-024), y aprovecharemos su límite nativo de intentos contra fuerza bruta. FastAPI solo agregará el bloqueo de cuenta durante 15 minutos tras 5 intentos fallidos, usando intentos_login_fallidos y bloqueado_hasta. Los roles serán Cliente, Vendedor y Administrador, y no habrá auto-registro como Administrador.</t>
+    <t>Usaremos Supabase Auth (GoTrue) para registro, login, refresh de sesión, recuperación y cambio de contraseña (RF-001, RF-020, RF-023 y RF-024). La protección contra fuerza bruta es el límite nativo de GoTrue, que responde con HTTP 429; no implementamos en FastAPI bloqueo de cuenta, conteo de intentos ni campos como intentos_login_fallidos o bloqueado_hasta, que quedan fuera del MVP. Los roles serán Cliente, Vendedor y Administrador, los permisos se gestionan con roles, RLS, policies y grants, y no habrá auto-registro como Administrador.</t>
   </si>
   <si>
     <t>Semanas 5-6</t>
@@ -1211,13 +1211,13 @@
     <t>2.1, 2.2, 3.1, 5.1</t>
   </si>
   <si>
-    <t>Autenticación configurada en Supabase Auth, perfiles con rol y regla de bloqueo en FastAPI.</t>
-  </si>
-  <si>
-    <t>Las contraseñas se guardan con hash en Supabase Auth, los roles restringen funciones, los tokens se validan y expiran, y la cuenta se bloquea al quinto intento fallido.</t>
-  </si>
-  <si>
-    <t>Controlaremos intentos fallidos, errores de autorización y exposición de secretos. Dejamos fuera el rate limiting propio con Redis porque no aporta valor con el tráfico esperado del MVP.</t>
+    <t>Autenticación y autorización configuradas en Supabase Auth (GoTrue), con perfiles por rol, RLS, policies y grants.</t>
+  </si>
+  <si>
+    <t>Las contraseñas se guardan con hash en Supabase Auth, los roles y las policies restringen las funciones, los tokens se validan y expiran, y GoTrue aplica su límite nativo de intentos con respuesta HTTP 429.</t>
+  </si>
+  <si>
+    <t>Controlaremos los errores de autorización y la exposición de secretos. La protección contra fuerza bruta queda a cargo del límite nativo de GoTrue y dejamos fuera el rate limiting propio con Redis porque no aporta valor con el tráfico esperado del MVP.</t>
   </si>
   <si>
     <t>3.3</t>
@@ -1226,10 +1226,10 @@
     <t>Servicios de Cliente, Vendedor y Administración</t>
   </si>
   <si>
-    <t>Dejar disponibles los datos y operaciones de cada rol, tanto con PostgREST como con FastAPI.</t>
-  </si>
-  <si>
-    <t>Definiremos qué consultas van directo a PostgREST (listados, catálogo, CRUD simples) y cuáles a FastAPI, y desarrollaremos lo necesario para catálogo, carrito, pedidos, productos, stock y usuarios (RF-002, RF-003, RF-004 y RF-017). Categorías, regiones y comunas quedan como consultas para los combobox (RF-018). Revisaremos de nuevo las políticas RLS ya creadas en Supabase para que cada rol vea solo lo suyo. Las eliminaciones serán lógicas y la activación de la cuenta de un productor será un paso manual del administrador.</t>
+    <t>Dejar disponibles los datos y operaciones de cada rol con PostgREST, RLS, policies y grants, y reservar FastAPI para la integración con Webpay.</t>
+  </si>
+  <si>
+    <t>Definiremos qué consultas van directo a PostgREST (listados, catálogo y CRUD simples), que será la vía principal, y qué resuelve FastAPI (solo la lógica de la integración con Webpay). Desarrollaremos lo necesario para catálogo, carrito, pedidos, productos, stock, reclamos (RF-027) y usuarios (RF-002, RF-003, RF-004 y RF-017). Categorías, regiones y comunas quedan como consultas para los combobox (RF-018). Revisaremos las políticas RLS, policies y grants ya creados en Supabase para que cada rol vea solo lo suyo. Las eliminaciones serán lógicas, la aprobación o el rechazo de una postulación y el registro del Código de Comercio Mall serán dos pasos distintos, y las consultas de visualización del frontend excluirán a los productores y productos que no puedan operar por falta del Código de Comercio registrado.</t>
   </si>
   <si>
     <t>Semanas 6-8</t>
@@ -1238,7 +1238,7 @@
     <t>3.2, 3.7</t>
   </si>
   <si>
-    <t>Consultas PostgREST, endpoints FastAPI y políticas RLS revisadas.</t>
+    <t>Consultas PostgREST, endpoints de FastAPI para Webpay y políticas RLS revisadas.</t>
   </si>
   <si>
     <t>CRUD y consultas principales funcionan con validaciones de rol y datos, y cada rol solo accede a lo que le corresponde.</t>
@@ -1253,10 +1253,10 @@
     <t>Pagos con Webpay Mall (Split Payment)</t>
   </si>
   <si>
-    <t>Reemplazar la confirmación simulada por un flujo real con Webpay Mall, donde la pasarela captura y dispersa el pago en tiempo real sin custodia de fondos.</t>
-  </si>
-  <si>
-    <t>Integraremos Webpay Mall (Split Payment) de Transbank en ambiente de integración: create -&gt; redirección -&gt; token_ws -&gt; commit, guardando cada pago en payments con idempotencia por buy_order y token_ws (RF-005). La pasarela captura y dispersa el pago en tiempo real y Transbank deposita directo en la cuenta bancaria del comercio: CuTuCo no retiene saldos ni ejecuta payouts. Los descuentos de la liquidación (fee base de 5% y tarifa fija de delivery de 3.500 CLP, RF-014; el fee se revisará según el flujo de caja) se aplican en el Split Payment. La cuenta bancaria de destino se inscribe en Transbank y se valida con el certificado de titularidad bancaria; los datos bancarios que se almacenan se guardan cifrados. Los reembolsos posventa se gestionan con la pasarela.</t>
+    <t>Reemplazar la confirmación simulada por un flujo real con Webpay Mall (Split Payment), en el que la pasarela captura y dispersa el pago en tiempo real hacia la cuenta de cada comercio.</t>
+  </si>
+  <si>
+    <t>Integraremos Webpay Mall (Split Payment) de Transbank en ambiente de integración: create -&gt; redirección -&gt; token_ws -&gt; commit, guardando cada pago en payments con idempotencia por buy_order y token_ws (RF-005). La pasarela captura y dispersa el pago en tiempo real y Transbank deposita directo en la cuenta bancaria del comercio, de modo que CuTuCo no administra fondos de terceros. El fee base de 5% y la tarifa fija de delivery de 3.500 CLP (RF-014; el fee se revisará según el flujo de caja) se configuran en el Split Payment. La tramitación para habilitar la cuenta de Transbank es un proceso legal y administrativo que queda fuera del flujo de la plataforma; los datos bancarios que la aplicación recibe quedan protegidos con RLS, policies y permisos de acceso.</t>
   </si>
   <si>
     <t>Semanas 8-9</t>
@@ -1265,13 +1265,13 @@
     <t>3.3, 3.7, 5.4</t>
   </si>
   <si>
-    <t>Flujo Webpay Mall (Split Payment), tabla payments, tabla productores con rut_oficial y codigo_comercio_mall, y datos bancarios cifrados.</t>
-  </si>
-  <si>
-    <t>Una compra de prueba crea, valida y registra el pago sin duplicar la orden, y la pasarela ejecuta la dispersión (Split Payment) con el descuento calculado; si corresponde, el reembolso queda registrado.</t>
-  </si>
-  <si>
-    <t>Protegeremos credenciales y trataremos fallos de retorno/commit como escenarios controlados. Al no custodiar fondos, CuTuCo elimina la responsabilidad legal de custodia de dinero de terceros. Evaluamos la Ley Fintech y la descartamos: apunta a activos financieros y criptoactivos.</t>
+    <t>Flujo Webpay Mall (Split Payment), tabla payments y tabla productores con rut_oficial y codigo_comercio_mall.</t>
+  </si>
+  <si>
+    <t>Una compra de prueba crea, valida y registra el pago sin duplicar la orden, y la pasarela ejecuta la dispersión (Split Payment) con el descuento configurado.</t>
+  </si>
+  <si>
+    <t>Protegeremos las credenciales y trataremos los fallos de retorno y de commit como escenarios controlados. Como la pasarela dispersa el pago directo a cada comercio, CuTuCo no administra fondos de terceros y reduce su exposición legal. Evaluamos la Ley Fintech y la descartamos: apunta a activos financieros y criptoactivos.</t>
   </si>
   <si>
     <t>3.5</t>
@@ -1283,16 +1283,16 @@
     <t>Agregar mecanismos de confianza y respaldo en la entrega.</t>
   </si>
   <si>
-    <t>Implementaremos calificaciones simples de 1 a 5 que se promedian por vendedor (RF-006), un código de verificación que valida la entrega y reemplaza las dos fotos de evidencia (RF-007), y sanciones manuales: conteo de amonestaciones con su duración, suspensión y un botón de Ban Permanente (RF-026). La moderación usará una lista de palabras prohibidas revisada con el operador LIKE; el administrador decide qué hacer con cada coincidencia. No habrá score 40/40/20, pausa automática ni sello “Cosecha del día”.</t>
+    <t>Implementaremos calificaciones simples de 1 a 5 que se promedian por vendedor (RF-006), un código de verificación que valida la entrega y reemplaza las dos fotos de evidencia (RF-007) y sanciones con su duración, suspensión, baneo permanente y apelaciones (RF-026). La validación de palabras prohibidas es automática: triggers de PostgreSQL, incluida la lógica BEFORE INSERT ya existente, rechazan el registro o la edición cuando el texto coincide con la lista, sin intervención operativa del administrador ni revisión manual con el operador LIKE. El módulo de sanciones se conecta con la gestión de reclamos (RF-027): un reclamo resuelto puede derivar en una amonestación o una suspensión. No habrá score 40/40/20, pausa automática ni sello “Cosecha del día”.</t>
   </si>
   <si>
     <t>3.3, 5.1</t>
   </si>
   <si>
-    <t>Calificaciones, sanciones y códigos de entrega persistidos.</t>
-  </si>
-  <si>
-    <t>El promedio de calificaciones se calcula bien, el administrador puede amonestar, suspender o banear, y el pedido solo pasa a Entregado con el código correcto.</t>
+    <t>Calificaciones, sanciones con apelaciones, reclamos y códigos de entrega persistidos.</t>
+  </si>
+  <si>
+    <t>El promedio de calificaciones se calcula bien, el administrador puede amonestar, suspender, banear y resolver apelaciones, el pedido solo pasa a Entregado con el código correcto y los triggers rechazan de forma automática las palabras prohibidas.</t>
   </si>
   <si>
     <t>Probaremos código incorrecto, calificaciones en los extremos (1 y 5) y las reglas de amonestación.</t>
@@ -1307,7 +1307,7 @@
     <t>Completar las reglas de negocio adicionales del alcance.</t>
   </si>
   <si>
-    <t>Implementaremos la restricción de venta por región, que compara la región del productor con la del cliente sin usar geolocalización (RF-009); los estados de delivery Preparación -&gt; En Tránsito -&gt; Entregado con código de verificación (RF-025); los correos (RF-012); y los datos del panel administrativo (RF-011). Los correos de autenticación (bienvenida, verificación y recuperar contraseña) saldrán por el SMTP de Resend configurado en Supabase Auth, y los de negocio (confirmación de pago, aprobación o rechazo de productor y reembolso) por la API de Resend.</t>
+    <t>Implementaremos la restricción de venta por región, que compara la región del productor con la del cliente sin usar geolocalización (RF-009); los estados de delivery Preparación -&gt; En Tránsito -&gt; Entregado con código de verificación (RF-025); los correos del MVP (RF-012); y los datos del panel administrativo (RF-011). Los correos de autenticación (bienvenida, verificación de cuenta y recuperación de contraseña) los envía Supabase Auth a través del SMTP de Resend. Por la API de Resend salen solo dos correos de negocio: el detalle de la compra al comprador y el aviso de nuevo pedido al vendedor. Los avisos automáticos de aprobación o rechazo de postulaciones quedan fuera del MVP.</t>
   </si>
   <si>
     <t>Semanas 7-10</t>
@@ -1367,7 +1367,7 @@
     <t>Establecer la nueva base frontend.</t>
   </si>
   <si>
-    <t>Prepararemos estructura de proyecto, rutas, componentes base, manejo de estados, Vuelidate para formularios y la conexión con Supabase y con la API de FastAPI.</t>
+    <t>Prepararemos estructura de proyecto, rutas, componentes base, manejo de estados, Vuelidate para formularios y la conexión con Supabase (PostgREST y Auth) y con la API de FastAPI de la integración con Webpay.</t>
   </si>
   <si>
     <t>2.3, 2.4</t>
@@ -1442,7 +1442,7 @@
     <t>Permitir administración y monitoreo del marketplace.</t>
   </si>
   <si>
-    <t>Construiremos el CRUD de usuarios y productos, la aprobación de productores (el administrador revisa la documentación KYB y, al aprobar, ingresa el Código de Comercio Mall obligatorio; se crea la ficha en productores con rut_oficial y codigo_comercio_mall y el usuario es promovido a rol vendedor), la moderación con lista de palabras prohibadas, las sanciones (amonestar, suspender o Ban Permanente) y la gestión de reembolsos (RF-004, RF-011 y RF-026). El dashboard queda reducido a esas acciones; ventas por región y ticket promedio no se incluyen en esta versión.</t>
+    <t>Construiremos el panel de administración con un alcance acotado: administración de usuarios limitada a listar, ver el detalle y activar o desactivar cuentas de clientes (las suspensiones y los baneos son del módulo de sanciones); administración de productos limitada a listar, visualizar y eliminar con baja lógica, sin edición; aprobación o rechazo de postulaciones revisando la documentación KYB; registro del Código de Comercio Mall como paso posterior e independiente de la aprobación; gestión de reclamos (RF-027) con su bandeja, estados, resolución y apelaciones; y sanciones (amonestar, suspender o baneo permanente) (RF-004, RF-011, RF-026 y RF-027). No administramos regiones ni comunas porque son valores fijos en la base de datos. Las consultas de visualización del frontend excluyen a los productores y productos que no puedan operar por falta del Código de Comercio registrado. El dashboard queda reducido a esas acciones; ventas por región y ticket promedio no se incluyen en esta versión.</t>
   </si>
   <si>
     <t>Semanas 8-10</t>
@@ -1454,7 +1454,7 @@
     <t>Panel admin y dashboard.</t>
   </si>
   <si>
-    <t>El administrador puede aprobar productores, aplicar sanciones y gestionar reembolsos desde el panel, y solo él accede a esas rutas.</t>
+    <t>El administrador puede aprobar o rechazar postulaciones, registrar el Código de Comercio Mall, gestionar reclamos y apelaciones y aplicar sanciones desde el panel, y solo él accede a esas rutas.</t>
   </si>
   <si>
     <t>Protegemos rutas administrativas y verificamos consistencia de datos.</t>
@@ -1469,7 +1469,7 @@
     <t>Cerrar la experiencia de compra y postcompra.</t>
   </si>
   <si>
-    <t>Conectaremos el checkout con Webpay Mall (redirección y retorno), el seguimiento web del pedido con los estados Preparación, En Tránsito y Entregado, el código de verificación y la calificación de 1 a 5 que deja el cliente al recibir. No habrá mapa ni GPS en tiempo real.</t>
+    <t>Conectaremos el checkout con Webpay Mall (redirección y retorno), el seguimiento web del pedido con los estados Preparación, En Tránsito y Entregado, el código de verificación, la calificación de 1 a 5 que deja el cliente al recibir y el registro de reclamos sobre el pedido (RF-027), con su seguimiento, su resolución y su apelación. No habrá mapa ni GPS en tiempo real.</t>
   </si>
   <si>
     <t>3.4, 3.5, 3.6</t>
@@ -1595,7 +1595,7 @@
     <t>Evitar que credenciales de servicios queden escritas en código.</t>
   </si>
   <si>
-    <t>Gestionaremos las credenciales de Webpay Mall, la API key de Resend, la clave con que ciframos los datos bancarios y otras variables protegidas mediante GCP Secret Manager/env vars.</t>
+    <t>Gestionaremos las credenciales de Webpay Mall, la API key de Resend y las demás variables protegidas mediante GCP Secret Manager o variables de entorno.</t>
   </si>
   <si>
     <t>3.4, 5.2</t>
@@ -1649,7 +1649,7 @@
     <t>Verificar cada unidad crítica en backend y frontend.</t>
   </si>
   <si>
-    <t>Cubriremos validadores, reglas de negocio (cobertura regional, bloqueo de cuenta, cálculo de fee y tarifa, promedio de calificaciones y código de entrega), autenticación, pagos y componentes importantes del frontend.</t>
+    <t>Cubriremos validadores, reglas de negocio (cobertura regional, cálculo del fee y de la tarifa de delivery, promedio de calificaciones, código de entrega, validación automática de palabras prohibidas por triggers y gestión de reclamos), autenticación y permisos, pagos y componentes importantes del frontend.</t>
   </si>
   <si>
     <t>Semanas 7-11</t>
@@ -1676,7 +1676,7 @@
     <t>Verificar comunicación entre servicios y base de datos.</t>
   </si>
   <si>
-    <t>Probaremos endpoints de FastAPI, consultas a PostgREST con sus políticas RLS, persistencia, reglas de autorización y escenarios de error.</t>
+    <t>Probaremos los endpoints de FastAPI de la integración con Webpay, las consultas a PostgREST con sus políticas RLS, la persistencia, los triggers de palabras prohibidas, las reglas de autorización y los escenarios de error.</t>
   </si>
   <si>
     <t>Semanas 8-11</t>
@@ -1703,7 +1703,7 @@
     <t>Validar la solución completa desde la interfaz.</t>
   </si>
   <si>
-    <t>Ejecutaremos el flujo completo: invitado navega -&gt; login en checkout -&gt; pago con Webpay Mall -&gt; dispersión (Split Payment) -&gt; preparación y tránsito -&gt; código de entrega -&gt; calificación -&gt; reembolso gestionado por el administrador cuando corresponda. También probaremos el registro y aprobación de un productor y las sanciones.</t>
+    <t>Ejecutaremos el flujo completo: invitado navega -&gt; login en checkout -&gt; pago con Webpay Mall -&gt; dispersión (Split Payment) -&gt; preparación y tránsito -&gt; código de entrega -&gt; calificación -&gt; reclamo gestionado por el administrador cuando corresponda, con su resolución y su apelación. También probaremos el registro y la aprobación de una postulación, el registro del Código de Comercio Mall y las sanciones.</t>
   </si>
   <si>
     <t>Semanas 9-11</t>
@@ -1730,7 +1730,7 @@
     <t>Confirmar que el producto construido corresponde a lo planificado.</t>
   </si>
   <si>
-    <t>Compararemos lo construido con los 21 requerimientos que quedan, la EDT y los hitos, y revisaremos que no haya funciones de las descartadas (por ejemplo historial de precios o alertas de stock) sin un cambio registrado.</t>
+    <t>Compararemos lo construido con los 22 requerimientos vigentes (los 21 anteriores más RF-027 Gestión de Reclamos), la EDT y los hitos, y revisaremos que no haya funciones de las descartadas (por ejemplo historial de precios o alertas de stock) sin un cambio registrado.</t>
   </si>
   <si>
     <t>Semana 11</t>
